--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21258,21 +21246,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2023-01-03 to 2026-03-22 | Publication days: 430</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21280,22 +21268,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -21214,15 +21214,17 @@
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="B1176" t="inlineStr"/>
+      <c r="B1176" t="n">
+        <v>-3</v>
+      </c>
       <c r="C1176" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D1176" t="n">
-        <v>-1.433333333333333</v>
+        <v>-1.466666666666667</v>
       </c>
       <c r="E1176" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21255,7 +21257,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-22 | Publication days: 430</t>
+          <t>Coverage: 2023-01-03 to 2026-03-22 | Publication days: 431</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1176"/>
+  <dimension ref="A1:E1177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21225,6 +21225,23 @@
       </c>
       <c r="E1176" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr"/>
+      <c r="C1177" t="n">
+        <v>-2.285714285714286</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>-1.466666666666667</v>
+      </c>
+      <c r="E1177" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21257,7 +21274,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-22 | Publication days: 431</t>
+          <t>Coverage: 2023-01-03 to 2026-03-23 | Publication days: 431</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1177"/>
+  <dimension ref="A1:E1178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21241,6 +21241,23 @@
         <v>-1.466666666666667</v>
       </c>
       <c r="E1177" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr"/>
+      <c r="C1178" t="n">
+        <v>-2.428571428571428</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>-1.466666666666667</v>
+      </c>
+      <c r="E1178" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21274,7 +21291,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-23 | Publication days: 431</t>
+          <t>Coverage: 2023-01-03 to 2026-03-24 | Publication days: 431</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1178"/>
+  <dimension ref="A1:E1179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21258,6 +21258,23 @@
         <v>-1.466666666666667</v>
       </c>
       <c r="E1178" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr"/>
+      <c r="C1179" t="n">
+        <v>-2.571428571428572</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E1179" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21291,7 +21308,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-24 | Publication days: 431</t>
+          <t>Coverage: 2023-01-03 to 2026-03-25 | Publication days: 431</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21299,21 +21311,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2023-01-03 to 2026-03-25 | Publication days: 431</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21321,22 +21333,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1179"/>
+  <dimension ref="A1:E1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21287,6 +21275,23 @@
         <v>-1.5</v>
       </c>
       <c r="E1179" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr"/>
+      <c r="C1180" t="n">
+        <v>-2.714285714285714</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="E1180" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21311,21 +21316,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2023-01-03 to 2026-03-25 | Publication days: 431</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2023-01-03 to 2026-03-26 | Publication days: 431</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21333,22 +21338,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -42,7 +45,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -50,14 +53,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -434,27 +446,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21316,21 +21328,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Coverage: 2023-01-03 to 2026-03-26 | Publication days: 431</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21338,22 +21350,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21328,21 +21316,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Coverage: 2023-01-03 to 2026-03-26 | Publication days: 431</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21350,22 +21338,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="daily_data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="variable_definitions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -53,23 +50,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1180"/>
+  <dimension ref="A1:E1181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,27 +434,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>raw</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>rolling7</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>rolling30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>publication</t>
         </is>
@@ -21262,15 +21250,17 @@
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="B1178" t="inlineStr"/>
+      <c r="B1178" t="n">
+        <v>2</v>
+      </c>
       <c r="C1178" t="n">
-        <v>-2.428571428571428</v>
+        <v>-1.714285714285714</v>
       </c>
       <c r="D1178" t="n">
-        <v>-1.466666666666667</v>
+        <v>-1.3</v>
       </c>
       <c r="E1178" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1179">
@@ -21281,10 +21271,10 @@
       </c>
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="n">
-        <v>-2.571428571428572</v>
+        <v>-1.142857142857143</v>
       </c>
       <c r="D1179" t="n">
-        <v>-1.5</v>
+        <v>-1.166666666666667</v>
       </c>
       <c r="E1179" t="b">
         <v>0</v>
@@ -21298,12 +21288,29 @@
       </c>
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="n">
-        <v>-2.714285714285714</v>
+        <v>-0.5714285714285714</v>
       </c>
       <c r="D1180" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="E1180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr"/>
+      <c r="C1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>-0.8333333333333334</v>
+      </c>
+      <c r="E1181" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21328,21 +21335,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Germany WDSI Data Workbook</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>Coverage: 2023-01-03 to 2026-03-26 | Publication days: 431</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage: 2023-01-03 to 2026-03-27 | Publication days: 432</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Locked to DSI-ICF/code/data_integration.executed.ipynb: publication-day raw score = same-day minimum, then forward-fill missing days, then compute rolling means on the filled daily path.</t>
         </is>
@@ -21350,22 +21357,22 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>variable</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>units_or_scale</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -21233,15 +21233,17 @@
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="B1177" t="inlineStr"/>
+      <c r="B1177" t="n">
+        <v>0</v>
+      </c>
       <c r="C1177" t="n">
-        <v>-2.285714285714286</v>
+        <v>-1.857142857142857</v>
       </c>
       <c r="D1177" t="n">
-        <v>-1.466666666666667</v>
+        <v>-1.366666666666667</v>
       </c>
       <c r="E1177" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1178">
@@ -21254,10 +21256,10 @@
         <v>2</v>
       </c>
       <c r="C1178" t="n">
-        <v>-1.714285714285714</v>
+        <v>-1.285714285714286</v>
       </c>
       <c r="D1178" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="E1178" t="b">
         <v>1</v>
@@ -21271,10 +21273,10 @@
       </c>
       <c r="B1179" t="inlineStr"/>
       <c r="C1179" t="n">
-        <v>-1.142857142857143</v>
+        <v>-0.7142857142857143</v>
       </c>
       <c r="D1179" t="n">
-        <v>-1.166666666666667</v>
+        <v>-1.066666666666667</v>
       </c>
       <c r="E1179" t="b">
         <v>0</v>
@@ -21288,10 +21290,10 @@
       </c>
       <c r="B1180" t="inlineStr"/>
       <c r="C1180" t="n">
-        <v>-0.5714285714285714</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="D1180" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="E1180" t="b">
         <v>0</v>
@@ -21305,10 +21307,10 @@
       </c>
       <c r="B1181" t="inlineStr"/>
       <c r="C1181" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="D1181" t="n">
-        <v>-0.8333333333333334</v>
+        <v>-0.7333333333333333</v>
       </c>
       <c r="E1181" t="b">
         <v>0</v>
@@ -21344,7 +21346,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-27 | Publication days: 432</t>
+          <t>Coverage: 2023-01-03 to 2026-03-27 | Publication days: 433</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1181"/>
+  <dimension ref="A1:E1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21305,7 +21305,9 @@
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="B1181" t="inlineStr"/>
+      <c r="B1181" t="n">
+        <v>2</v>
+      </c>
       <c r="C1181" t="n">
         <v>0.4285714285714285</v>
       </c>
@@ -21313,6 +21315,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E1181" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr"/>
+      <c r="C1182" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>-0.5666666666666667</v>
+      </c>
+      <c r="E1182" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21346,7 +21365,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-27 | Publication days: 433</t>
+          <t>Coverage: 2023-01-03 to 2026-03-28 | Publication days: 434</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1182"/>
+  <dimension ref="A1:E1183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21332,6 +21332,23 @@
         <v>-0.5666666666666667</v>
       </c>
       <c r="E1182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr"/>
+      <c r="C1183" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="E1183" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21365,7 +21382,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-28 | Publication days: 434</t>
+          <t>Coverage: 2023-01-03 to 2026-03-29 | Publication days: 434</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1183"/>
+  <dimension ref="A1:E1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21341,15 +21341,36 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B1183" t="inlineStr"/>
+      <c r="B1183" t="n">
+        <v>0</v>
+      </c>
       <c r="C1183" t="n">
-        <v>1.714285714285714</v>
+        <v>1.428571428571429</v>
       </c>
       <c r="D1183" t="n">
-        <v>-0.5</v>
+        <v>-0.5666666666666667</v>
       </c>
       <c r="E1183" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>-0.4666666666666667</v>
+      </c>
+      <c r="E1184" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -21382,7 +21403,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-29 | Publication days: 434</t>
+          <t>Coverage: 2023-01-03 to 2026-03-30 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1184"/>
+  <dimension ref="A1:E1185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21341,17 +21341,15 @@
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="B1183" t="n">
-        <v>0</v>
-      </c>
+      <c r="B1183" t="inlineStr"/>
       <c r="C1183" t="n">
-        <v>1.428571428571429</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D1183" t="n">
-        <v>-0.5666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1183" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1184">
@@ -21361,15 +21359,34 @@
         </is>
       </c>
       <c r="B1184" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C1184" t="n">
-        <v>1.857142857142857</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="D1184" t="n">
-        <v>-0.4666666666666667</v>
+        <v>-0.5</v>
       </c>
       <c r="E1184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>1</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E1185" t="b">
         <v>1</v>
       </c>
     </row>
@@ -21403,7 +21420,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-30 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-03-31 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1185"/>
+  <dimension ref="A1:E1186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21388,6 +21388,23 @@
       </c>
       <c r="E1185" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr"/>
+      <c r="C1186" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E1186" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21420,7 +21437,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-03-31 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-01 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1186"/>
+  <dimension ref="A1:E1187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21404,6 +21404,23 @@
         <v>-0.7</v>
       </c>
       <c r="E1186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr"/>
+      <c r="C1187" t="n">
+        <v>-0.4285714285714285</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>-0.7333333333333333</v>
+      </c>
+      <c r="E1187" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21437,7 +21454,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-01 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-02 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1187"/>
+  <dimension ref="A1:E1188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21421,6 +21421,23 @@
         <v>-0.7333333333333333</v>
       </c>
       <c r="E1187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr"/>
+      <c r="C1188" t="n">
+        <v>-1.142857142857143</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>-0.7666666666666667</v>
+      </c>
+      <c r="E1188" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21454,7 +21471,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-02 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-03 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1188"/>
+  <dimension ref="A1:E1189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21438,6 +21438,23 @@
         <v>-0.7666666666666667</v>
       </c>
       <c r="E1188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr"/>
+      <c r="C1189" t="n">
+        <v>-1.857142857142857</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>-0.9333333333333333</v>
+      </c>
+      <c r="E1189" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21471,7 +21488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-03 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-04 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1189"/>
+  <dimension ref="A1:E1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21455,6 +21455,23 @@
         <v>-0.9333333333333333</v>
       </c>
       <c r="E1189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr"/>
+      <c r="C1190" t="n">
+        <v>-2.571428571428572</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>-1.033333333333333</v>
+      </c>
+      <c r="E1190" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21488,7 +21505,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-04 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-05 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1190"/>
+  <dimension ref="A1:E1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21472,6 +21472,23 @@
         <v>-1.033333333333333</v>
       </c>
       <c r="E1190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr"/>
+      <c r="C1191" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>-1.133333333333333</v>
+      </c>
+      <c r="E1191" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21505,7 +21522,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-05 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-06 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1191"/>
+  <dimension ref="A1:E1192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21489,6 +21489,23 @@
         <v>-1.133333333333333</v>
       </c>
       <c r="E1191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr"/>
+      <c r="C1192" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>-1.233333333333333</v>
+      </c>
+      <c r="E1192" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21522,7 +21539,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-06 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-07 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1192"/>
+  <dimension ref="A1:E1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21506,6 +21506,23 @@
         <v>-1.233333333333333</v>
       </c>
       <c r="E1192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr"/>
+      <c r="C1193" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>-1.333333333333333</v>
+      </c>
+      <c r="E1193" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21539,7 +21556,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-07 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-08 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1193"/>
+  <dimension ref="A1:E1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21523,6 +21523,23 @@
         <v>-1.333333333333333</v>
       </c>
       <c r="E1193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr"/>
+      <c r="C1194" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>-1.366666666666667</v>
+      </c>
+      <c r="E1194" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21556,7 +21573,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-08 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-09 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1194"/>
+  <dimension ref="A1:E1195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21540,6 +21540,23 @@
         <v>-1.366666666666667</v>
       </c>
       <c r="E1194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr"/>
+      <c r="C1195" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E1195" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21573,7 +21590,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-09 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-10 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1195"/>
+  <dimension ref="A1:E1196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21557,6 +21557,23 @@
         <v>-1.4</v>
       </c>
       <c r="E1195" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr"/>
+      <c r="C1196" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>-1.433333333333333</v>
+      </c>
+      <c r="E1196" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21590,7 +21607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-10 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-11 | Publication days: 436</t>
         </is>
       </c>
     </row>

--- a/data/DE.xlsx
+++ b/data/DE.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1196"/>
+  <dimension ref="A1:E1197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21574,6 +21574,23 @@
         <v>-1.433333333333333</v>
       </c>
       <c r="E1196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr"/>
+      <c r="C1197" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>-1.466666666666667</v>
+      </c>
+      <c r="E1197" t="b">
         <v>0</v>
       </c>
     </row>
@@ -21607,7 +21624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Coverage: 2023-01-03 to 2026-04-11 | Publication days: 436</t>
+          <t>Coverage: 2023-01-03 to 2026-04-12 | Publication days: 436</t>
         </is>
       </c>
     </row>
